--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/189.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/189.xlsx
@@ -426,13 +426,13 @@
         <v>3.447827402291807</v>
       </c>
       <c r="E2">
-        <v>-16.31944952558358</v>
+        <v>-16.63282445538838</v>
       </c>
       <c r="F2">
-        <v>-0.1854757505713311</v>
+        <v>-0.4853853403874893</v>
       </c>
       <c r="G2">
-        <v>-10.40456906204002</v>
+        <v>-12.44273952874772</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.297857565954975</v>
       </c>
       <c r="E3">
-        <v>-16.59220857201359</v>
+        <v>-17.36058192773906</v>
       </c>
       <c r="F3">
-        <v>-0.3719213721238326</v>
+        <v>-0.6553008904171267</v>
       </c>
       <c r="G3">
-        <v>-10.25867994121542</v>
+        <v>-12.01681136075617</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.197380740723444</v>
       </c>
       <c r="E4">
-        <v>-17.08733380611623</v>
+        <v>-17.21272725138862</v>
       </c>
       <c r="F4">
-        <v>0.1231689735073479</v>
+        <v>-0.401002038166512</v>
       </c>
       <c r="G4">
-        <v>-10.26372521261727</v>
+        <v>-12.17218519455078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.174740745939796</v>
       </c>
       <c r="E5">
-        <v>-16.79777412111777</v>
+        <v>-17.94165759850729</v>
       </c>
       <c r="F5">
-        <v>0.1495632440627486</v>
+        <v>0.04217120886161228</v>
       </c>
       <c r="G5">
-        <v>-9.989257813592911</v>
+        <v>-12.13173694915197</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.233663097206766</v>
       </c>
       <c r="E6">
-        <v>-16.55182364081318</v>
+        <v>-18.82421189786217</v>
       </c>
       <c r="F6">
-        <v>-0.1164578353048819</v>
+        <v>-0.3709869736934747</v>
       </c>
       <c r="G6">
-        <v>-8.501336431513014</v>
+        <v>-11.421346845153</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.384016570221885</v>
       </c>
       <c r="E7">
-        <v>-17.83630265071884</v>
+        <v>-19.1469381264928</v>
       </c>
       <c r="F7">
-        <v>0.4940307164754922</v>
+        <v>-0.06957886724565222</v>
       </c>
       <c r="G7">
-        <v>-9.356668840312354</v>
+        <v>-11.30263068211473</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.625698639507154</v>
       </c>
       <c r="E8">
-        <v>-18.32934478677796</v>
+        <v>-20.5349335237398</v>
       </c>
       <c r="F8">
-        <v>-0.2735378324281409</v>
+        <v>-0.3108615824960782</v>
       </c>
       <c r="G8">
-        <v>-8.777022111295823</v>
+        <v>-10.38828779907788</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.945739680516364</v>
       </c>
       <c r="E9">
-        <v>-19.72584918668537</v>
+        <v>-19.43349996169818</v>
       </c>
       <c r="F9">
-        <v>0.09618490536115404</v>
+        <v>-0.02067122741696661</v>
       </c>
       <c r="G9">
-        <v>-6.75921812074572</v>
+        <v>-10.43548955737681</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.330078095917478</v>
       </c>
       <c r="E10">
-        <v>-21.62908077110307</v>
+        <v>-20.47591845047184</v>
       </c>
       <c r="F10">
-        <v>0.27650972017437</v>
+        <v>-0.1869088261781742</v>
       </c>
       <c r="G10">
-        <v>-7.719915262423443</v>
+        <v>-10.05835883063412</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.757617617816749</v>
       </c>
       <c r="E11">
-        <v>-19.44096288686282</v>
+        <v>-21.05209884083778</v>
       </c>
       <c r="F11">
-        <v>0.4585484271439782</v>
+        <v>0.3510511892826864</v>
       </c>
       <c r="G11">
-        <v>-6.785947465429795</v>
+        <v>-9.427203323572066</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.193058212117196</v>
       </c>
       <c r="E12">
-        <v>-19.31807821619068</v>
+        <v>-21.26791685509533</v>
       </c>
       <c r="F12">
-        <v>-0.00250098843655946</v>
+        <v>-0.0185224423741047</v>
       </c>
       <c r="G12">
-        <v>-7.458782740831271</v>
+        <v>-9.040640852587988</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.608673792112095</v>
       </c>
       <c r="E13">
-        <v>-20.73380145978664</v>
+        <v>-22.80487187635063</v>
       </c>
       <c r="F13">
-        <v>0.315496003619726</v>
+        <v>0.2688514635354886</v>
       </c>
       <c r="G13">
-        <v>-6.585404548297364</v>
+        <v>-8.995759786712087</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.983061880178818</v>
       </c>
       <c r="E14">
-        <v>-22.17750161580199</v>
+        <v>-22.9245820867434</v>
       </c>
       <c r="F14">
-        <v>0.6924752398575446</v>
+        <v>0.3858633293853356</v>
       </c>
       <c r="G14">
-        <v>-5.697310980841397</v>
+        <v>-7.671227069177382</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.293386114166625</v>
       </c>
       <c r="E15">
-        <v>-21.87470972975312</v>
+        <v>-23.42448486092414</v>
       </c>
       <c r="F15">
-        <v>1.477297853394089</v>
+        <v>0.5216145226213129</v>
       </c>
       <c r="G15">
-        <v>-6.814563821071255</v>
+        <v>-7.297939885805781</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.528546571755018</v>
       </c>
       <c r="E16">
-        <v>-22.9744722848859</v>
+        <v>-24.51575199881853</v>
       </c>
       <c r="F16">
-        <v>1.14441344237469</v>
+        <v>1.00617880366512</v>
       </c>
       <c r="G16">
-        <v>-5.055048593495091</v>
+        <v>-7.429524139355193</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.685319402111996</v>
       </c>
       <c r="E17">
-        <v>-23.90531370258457</v>
+        <v>-25.51215213472624</v>
       </c>
       <c r="F17">
-        <v>1.807796566293424</v>
+        <v>1.144009199082124</v>
       </c>
       <c r="G17">
-        <v>-4.727900483304312</v>
+        <v>-6.938705968248386</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.758376374033936</v>
       </c>
       <c r="E18">
-        <v>-25.06500155426085</v>
+        <v>-25.32030333339129</v>
       </c>
       <c r="F18">
-        <v>2.054114926985468</v>
+        <v>1.154330656921006</v>
       </c>
       <c r="G18">
-        <v>-5.88662452750462</v>
+        <v>-7.24088925452752</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.747024895254991</v>
       </c>
       <c r="E19">
-        <v>-26.51952929162854</v>
+        <v>-26.42697181138577</v>
       </c>
       <c r="F19">
-        <v>2.361863357534318</v>
+        <v>1.371038196432579</v>
       </c>
       <c r="G19">
-        <v>-5.306090572283564</v>
+        <v>-6.951478052938894</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.657942373966441</v>
       </c>
       <c r="E20">
-        <v>-26.12723664529208</v>
+        <v>-26.89656550903317</v>
       </c>
       <c r="F20">
-        <v>1.73059272435251</v>
+        <v>1.634536897058685</v>
       </c>
       <c r="G20">
-        <v>-3.844650243972298</v>
+        <v>-6.820807509958321</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.496236293658527</v>
       </c>
       <c r="E21">
-        <v>-26.96991320253541</v>
+        <v>-26.73728549276138</v>
       </c>
       <c r="F21">
-        <v>2.066134538000089</v>
+        <v>1.718863041928869</v>
       </c>
       <c r="G21">
-        <v>-5.635827529086053</v>
+        <v>-6.386043495922454</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.267422955218228</v>
       </c>
       <c r="E22">
-        <v>-25.22180902372445</v>
+        <v>-27.62918203399408</v>
       </c>
       <c r="F22">
-        <v>2.025491519749134</v>
+        <v>1.692832424663298</v>
       </c>
       <c r="G22">
-        <v>-3.318170876316462</v>
+        <v>-6.617530082210452</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.983518962140987</v>
       </c>
       <c r="E23">
-        <v>-26.89066943587518</v>
+        <v>-28.11601563218868</v>
       </c>
       <c r="F23">
-        <v>2.457910901154115</v>
+        <v>1.880149488723544</v>
       </c>
       <c r="G23">
-        <v>-4.202967140415316</v>
+        <v>-6.841640773036954</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.655749871671438</v>
       </c>
       <c r="E24">
-        <v>-26.35011907900159</v>
+        <v>-28.17921954391374</v>
       </c>
       <c r="F24">
-        <v>1.37969629252664</v>
+        <v>1.829027622827175</v>
       </c>
       <c r="G24">
-        <v>-4.705372220909572</v>
+        <v>-6.054767135444203</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.291801844428922</v>
       </c>
       <c r="E25">
-        <v>-27.521096416379</v>
+        <v>-28.71122467033485</v>
       </c>
       <c r="F25">
-        <v>1.927089755970581</v>
+        <v>2.11420635511935</v>
       </c>
       <c r="G25">
-        <v>-4.903783146714711</v>
+        <v>-6.266059393942648</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.902918634503403</v>
       </c>
       <c r="E26">
-        <v>-27.57798763533737</v>
+        <v>-28.60918003704601</v>
       </c>
       <c r="F26">
-        <v>1.622858573414018</v>
+        <v>1.805606362880422</v>
       </c>
       <c r="G26">
-        <v>-3.972387643605078</v>
+        <v>-6.599034064282544</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.500651083017765</v>
       </c>
       <c r="E27">
-        <v>-27.60214251569428</v>
+        <v>-28.8414364119514</v>
       </c>
       <c r="F27">
-        <v>2.225641651613551</v>
+        <v>1.780268260763591</v>
       </c>
       <c r="G27">
-        <v>-4.2814403118782</v>
+        <v>-6.504074376034089</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.090297942133171</v>
       </c>
       <c r="E28">
-        <v>-26.98519680231129</v>
+        <v>-28.40236915758971</v>
       </c>
       <c r="F28">
-        <v>2.483903413519158</v>
+        <v>1.67051952030149</v>
       </c>
       <c r="G28">
-        <v>-4.362833384506721</v>
+        <v>-7.288885543755874</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.677927685489167</v>
       </c>
       <c r="E29">
-        <v>-25.69219973279721</v>
+        <v>-28.31292726746421</v>
       </c>
       <c r="F29">
-        <v>1.78361155160129</v>
+        <v>1.954208848003431</v>
       </c>
       <c r="G29">
-        <v>-5.152140273070836</v>
+        <v>-6.871720389806772</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.273114601720855</v>
       </c>
       <c r="E30">
-        <v>-27.6777816170444</v>
+        <v>-27.82627480822991</v>
       </c>
       <c r="F30">
-        <v>2.062559304289607</v>
+        <v>1.737403561138328</v>
       </c>
       <c r="G30">
-        <v>-4.160204823684549</v>
+        <v>-6.647924200806501</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.878640382490738</v>
       </c>
       <c r="E31">
-        <v>-26.55024140234856</v>
+        <v>-28.2764322954364</v>
       </c>
       <c r="F31">
-        <v>1.879191896005908</v>
+        <v>1.682005662708708</v>
       </c>
       <c r="G31">
-        <v>-4.978806729725675</v>
+        <v>-7.01390501017293</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.494547127394845</v>
       </c>
       <c r="E32">
-        <v>-27.13382584771704</v>
+        <v>-27.76001417654968</v>
       </c>
       <c r="F32">
-        <v>1.712701645186846</v>
+        <v>1.826534236944749</v>
       </c>
       <c r="G32">
-        <v>-4.926036633829693</v>
+        <v>-7.31179782943317</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.127024862082222</v>
       </c>
       <c r="E33">
-        <v>-25.92127259047521</v>
+        <v>-27.70000283900004</v>
       </c>
       <c r="F33">
-        <v>1.784830908418211</v>
+        <v>1.560248908375625</v>
       </c>
       <c r="G33">
-        <v>-6.023883056108343</v>
+        <v>-7.164819539126147</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.775687485461218</v>
       </c>
       <c r="E34">
-        <v>-26.01928688189723</v>
+        <v>-27.57023488783623</v>
       </c>
       <c r="F34">
-        <v>1.492162078069923</v>
+        <v>1.55952822873519</v>
       </c>
       <c r="G34">
-        <v>-4.993353266825233</v>
+        <v>-7.233860966347648</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.436197713905241</v>
       </c>
       <c r="E35">
-        <v>-25.96195640096012</v>
+        <v>-26.9998418872521</v>
       </c>
       <c r="F35">
-        <v>1.903257625792039</v>
+        <v>1.725282889300565</v>
       </c>
       <c r="G35">
-        <v>-5.34635673767772</v>
+        <v>-7.80006025938366</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.111526929137089</v>
       </c>
       <c r="E36">
-        <v>-23.56267577374221</v>
+        <v>-27.42405574686864</v>
       </c>
       <c r="F36">
-        <v>1.676821739501989</v>
+        <v>1.487659072868305</v>
       </c>
       <c r="G36">
-        <v>-5.330333697267647</v>
+        <v>-7.40927684283701</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.8009423000605634</v>
       </c>
       <c r="E37">
-        <v>-25.17557783258015</v>
+        <v>-26.28964583710317</v>
       </c>
       <c r="F37">
-        <v>1.444164814016914</v>
+        <v>1.571682035269064</v>
       </c>
       <c r="G37">
-        <v>-6.156013549671735</v>
+        <v>-6.890736163384346</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.5021362521765589</v>
       </c>
       <c r="E38">
-        <v>-22.47173921445037</v>
+        <v>-25.69949510442356</v>
       </c>
       <c r="F38">
-        <v>2.669124708050322</v>
+        <v>1.616715400754857</v>
       </c>
       <c r="G38">
-        <v>-5.414769161246759</v>
+        <v>-7.520627042050396</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.2192548274124499</v>
       </c>
       <c r="E39">
-        <v>-23.2998929555511</v>
+        <v>-25.22327624930294</v>
       </c>
       <c r="F39">
-        <v>1.802370759805087</v>
+        <v>2.020953723116599</v>
       </c>
       <c r="G39">
-        <v>-5.556000344497606</v>
+        <v>-7.267820542489491</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.04453861754850437</v>
       </c>
       <c r="E40">
-        <v>-23.46077605162161</v>
+        <v>-24.56784756380277</v>
       </c>
       <c r="F40">
-        <v>1.855976071175049</v>
+        <v>1.876330714996638</v>
       </c>
       <c r="G40">
-        <v>-6.715770521088325</v>
+        <v>-7.611524690922165</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.2872049726725964</v>
       </c>
       <c r="E41">
-        <v>-23.0517506938268</v>
+        <v>-24.82488374847814</v>
       </c>
       <c r="F41">
-        <v>2.304111238945942</v>
+        <v>1.751277058400414</v>
       </c>
       <c r="G41">
-        <v>-5.452860298221613</v>
+        <v>-7.439293559241582</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.5037096366428009</v>
       </c>
       <c r="E42">
-        <v>-24.48388512722655</v>
+        <v>-23.88595447620178</v>
       </c>
       <c r="F42">
-        <v>2.019341720150751</v>
+        <v>1.703326182921962</v>
       </c>
       <c r="G42">
-        <v>-5.578392874525237</v>
+        <v>-8.298423163774466</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.6891268417148684</v>
       </c>
       <c r="E43">
-        <v>-23.09859322896214</v>
+        <v>-24.2283342820257</v>
       </c>
       <c r="F43">
-        <v>2.583514593705799</v>
+        <v>1.823631637565339</v>
       </c>
       <c r="G43">
-        <v>-5.933703795618595</v>
+        <v>-7.627253092779243</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.8408054376134307</v>
       </c>
       <c r="E44">
-        <v>-21.51614515782578</v>
+        <v>-22.79430241801673</v>
       </c>
       <c r="F44">
-        <v>2.244024781016477</v>
+        <v>1.750075925666355</v>
       </c>
       <c r="G44">
-        <v>-7.991982515931828</v>
+        <v>-8.004589073345374</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.9563535529937756</v>
       </c>
       <c r="E45">
-        <v>-22.78987809891123</v>
+        <v>-22.56699566520172</v>
       </c>
       <c r="F45">
-        <v>2.082413614199905</v>
+        <v>1.783775568347044</v>
       </c>
       <c r="G45">
-        <v>-6.99432975439922</v>
+        <v>-7.09231197072503</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.034444148203073</v>
       </c>
       <c r="E46">
-        <v>-22.3893391014068</v>
+        <v>-22.88070117360907</v>
       </c>
       <c r="F46">
-        <v>2.030256289050037</v>
+        <v>1.521227833499352</v>
       </c>
       <c r="G46">
-        <v>-6.922646511837381</v>
+        <v>-7.652145084689023</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.07577417143975</v>
       </c>
       <c r="E47">
-        <v>-20.51065184611067</v>
+        <v>-22.14620080346097</v>
       </c>
       <c r="F47">
-        <v>2.28878312852454</v>
+        <v>1.795563236488881</v>
       </c>
       <c r="G47">
-        <v>-7.465049603537111</v>
+        <v>-8.07705029410894</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.082048188114565</v>
       </c>
       <c r="E48">
-        <v>-20.32370285365201</v>
+        <v>-21.44285633448564</v>
       </c>
       <c r="F48">
-        <v>2.087784748439657</v>
+        <v>1.656879622646993</v>
       </c>
       <c r="G48">
-        <v>-6.356596193350637</v>
+        <v>-8.215609867109597</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.055496537675996</v>
       </c>
       <c r="E49">
-        <v>-20.00000300310973</v>
+        <v>-21.32184192357867</v>
       </c>
       <c r="F49">
-        <v>2.156068730187226</v>
+        <v>1.724621852113131</v>
       </c>
       <c r="G49">
-        <v>-7.260073865927597</v>
+        <v>-7.892709186845703</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9999563094402601</v>
       </c>
       <c r="E50">
-        <v>-19.44284220357601</v>
+        <v>-20.99952325760872</v>
       </c>
       <c r="F50">
-        <v>1.679739249494649</v>
+        <v>1.698283082173718</v>
       </c>
       <c r="G50">
-        <v>-6.900793600732652</v>
+        <v>-8.228706385262953</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.9192110933658704</v>
       </c>
       <c r="E51">
-        <v>-18.62925203488394</v>
+        <v>-20.09324881140167</v>
       </c>
       <c r="F51">
-        <v>2.350839444137863</v>
+        <v>1.707096911339505</v>
       </c>
       <c r="G51">
-        <v>-7.313529244750208</v>
+        <v>-8.246543604628547</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.8173515337585696</v>
       </c>
       <c r="E52">
-        <v>-19.63658843552017</v>
+        <v>-20.59568300255269</v>
       </c>
       <c r="F52">
-        <v>1.751485806985919</v>
+        <v>1.573802655820231</v>
       </c>
       <c r="G52">
-        <v>-8.366679991703158</v>
+        <v>-7.918988297336438</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6990398691655003</v>
       </c>
       <c r="E53">
-        <v>-18.64687685572179</v>
+        <v>-20.2857315990977</v>
       </c>
       <c r="F53">
-        <v>2.253519528187365</v>
+        <v>1.618917201311498</v>
       </c>
       <c r="G53">
-        <v>-7.453694432337412</v>
+        <v>-9.165127296501202</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.5675037359849585</v>
       </c>
       <c r="E54">
-        <v>-18.70105551874956</v>
+        <v>-20.05327144286196</v>
       </c>
       <c r="F54">
-        <v>2.524112367251046</v>
+        <v>1.48427270692566</v>
       </c>
       <c r="G54">
-        <v>-8.45674669364457</v>
+        <v>-9.123258827066039</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.4270080704554396</v>
       </c>
       <c r="E55">
-        <v>-18.96310925262543</v>
+        <v>-18.91275262166014</v>
       </c>
       <c r="F55">
-        <v>2.381348215582968</v>
+        <v>1.679697831124509</v>
       </c>
       <c r="G55">
-        <v>-9.032874312752856</v>
+        <v>-9.438098328941807</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.2814063492716389</v>
       </c>
       <c r="E56">
-        <v>-18.68221706687766</v>
+        <v>-19.44651026752222</v>
       </c>
       <c r="F56">
-        <v>2.190374737806764</v>
+        <v>1.7049945148712</v>
       </c>
       <c r="G56">
-        <v>-8.260815366448345</v>
+        <v>-9.041071223508093</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.1329179683296045</v>
       </c>
       <c r="E57">
-        <v>-17.38662971023118</v>
+        <v>-17.63882495619235</v>
       </c>
       <c r="F57">
-        <v>2.012671705823409</v>
+        <v>1.880118010762238</v>
       </c>
       <c r="G57">
-        <v>-7.81450085902596</v>
+        <v>-9.277080015002735</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.01543710271795262</v>
       </c>
       <c r="E58">
-        <v>-16.41833328401507</v>
+        <v>-17.9050584715773</v>
       </c>
       <c r="F58">
-        <v>2.431320307524251</v>
+        <v>1.799257755105367</v>
       </c>
       <c r="G58">
-        <v>-8.713628474764318</v>
+        <v>-9.265777812531663</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.1608810542709871</v>
       </c>
       <c r="E59">
-        <v>-15.9277365239201</v>
+        <v>-18.87985325799441</v>
       </c>
       <c r="F59">
-        <v>1.778550226770185</v>
+        <v>1.727282568210923</v>
       </c>
       <c r="G59">
-        <v>-9.144184785419771</v>
+        <v>-9.238157931097524</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.301743950239396</v>
       </c>
       <c r="E60">
-        <v>-17.29673950117892</v>
+        <v>-17.91868464986638</v>
       </c>
       <c r="F60">
-        <v>2.139459963761096</v>
+        <v>1.508306958750485</v>
       </c>
       <c r="G60">
-        <v>-9.162518586616256</v>
+        <v>-9.061093402929604</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.4359861423256933</v>
       </c>
       <c r="E61">
-        <v>-16.66494492152479</v>
+        <v>-18.11731257679082</v>
       </c>
       <c r="F61">
-        <v>2.115273292334156</v>
+        <v>1.50033972107036</v>
       </c>
       <c r="G61">
-        <v>-9.767404914824191</v>
+        <v>-8.939550034000803</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.5613387431661515</v>
       </c>
       <c r="E62">
-        <v>-15.38215503242399</v>
+        <v>-17.55663768142714</v>
       </c>
       <c r="F62">
-        <v>1.615177950855261</v>
+        <v>1.318476627990145</v>
       </c>
       <c r="G62">
-        <v>-9.855091334522866</v>
+        <v>-9.33079030583187</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.6766987301515078</v>
       </c>
       <c r="E63">
-        <v>-16.34730416920477</v>
+        <v>-17.65255981785761</v>
       </c>
       <c r="F63">
-        <v>1.428516953778031</v>
+        <v>1.588605581308258</v>
       </c>
       <c r="G63">
-        <v>-9.049516425178773</v>
+        <v>-9.45684925887624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.7817469426665682</v>
       </c>
       <c r="E64">
-        <v>-14.68528175280562</v>
+        <v>-17.74522145300256</v>
       </c>
       <c r="F64">
-        <v>1.187110811784588</v>
+        <v>1.403853142727079</v>
       </c>
       <c r="G64">
-        <v>-9.145568593455188</v>
+        <v>-9.318981589893291</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.8759861506705598</v>
       </c>
       <c r="E65">
-        <v>-17.10679265892719</v>
+        <v>-18.25125125251568</v>
       </c>
       <c r="F65">
-        <v>1.739464539236493</v>
+        <v>1.320680085281592</v>
       </c>
       <c r="G65">
-        <v>-8.416900967533902</v>
+        <v>-9.23063968217784</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.9596181980959031</v>
       </c>
       <c r="E66">
-        <v>-15.56918100894077</v>
+        <v>-16.30639846349348</v>
       </c>
       <c r="F66">
-        <v>1.669805467600277</v>
+        <v>1.45950286484715</v>
       </c>
       <c r="G66">
-        <v>-7.976323635531076</v>
+        <v>-8.898764112956981</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.03501375437322</v>
       </c>
       <c r="E67">
-        <v>-15.61173507919085</v>
+        <v>-16.88112974217696</v>
       </c>
       <c r="F67">
-        <v>1.568141592989499</v>
+        <v>1.313970309318916</v>
       </c>
       <c r="G67">
-        <v>-9.299694351581497</v>
+        <v>-9.626723282132861</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.104110545795309</v>
       </c>
       <c r="E68">
-        <v>-15.42010364460827</v>
+        <v>-17.10394877725037</v>
       </c>
       <c r="F68">
-        <v>1.75952262752788</v>
+        <v>1.363231662028597</v>
       </c>
       <c r="G68">
-        <v>-9.470538364681126</v>
+        <v>-9.707606530748336</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.168530179718611</v>
       </c>
       <c r="E69">
-        <v>-14.8609684304072</v>
+        <v>-17.14484542601365</v>
       </c>
       <c r="F69">
-        <v>1.73377365517926</v>
+        <v>1.110412273959382</v>
       </c>
       <c r="G69">
-        <v>-9.034708354981612</v>
+        <v>-9.547197357188489</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.232424632991139</v>
       </c>
       <c r="E70">
-        <v>-14.53025850210104</v>
+        <v>-16.75757032887768</v>
       </c>
       <c r="F70">
-        <v>2.193519220467791</v>
+        <v>1.151414803663152</v>
       </c>
       <c r="G70">
-        <v>-9.827822370915889</v>
+        <v>-9.370232145386748</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.299622998206204</v>
       </c>
       <c r="E71">
-        <v>-16.01006418137954</v>
+        <v>-16.95887458394064</v>
       </c>
       <c r="F71">
-        <v>2.19227004242437</v>
+        <v>0.9216869853143762</v>
       </c>
       <c r="G71">
-        <v>-8.513307364183019</v>
+        <v>-9.36740162895067</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.371704685362563</v>
       </c>
       <c r="E72">
-        <v>-14.56898601181464</v>
+        <v>-17.86406672485987</v>
       </c>
       <c r="F72">
-        <v>1.698738684245258</v>
+        <v>1.175260187720139</v>
       </c>
       <c r="G72">
-        <v>-8.14696239480727</v>
+        <v>-9.866085656258786</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.453059597489647</v>
       </c>
       <c r="E73">
-        <v>-17.07931387864865</v>
+        <v>-17.54357303391501</v>
       </c>
       <c r="F73">
-        <v>1.687789323915054</v>
+        <v>1.009296778569257</v>
       </c>
       <c r="G73">
-        <v>-7.59532950214405</v>
+        <v>-9.046315127642298</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.547358820025216</v>
       </c>
       <c r="E74">
-        <v>-16.80237505070956</v>
+        <v>-16.33389082919404</v>
       </c>
       <c r="F74">
-        <v>1.333324285317923</v>
+        <v>1.102186585649583</v>
       </c>
       <c r="G74">
-        <v>-7.375244434693302</v>
+        <v>-8.609445606643455</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.654214722311029</v>
       </c>
       <c r="E75">
-        <v>-17.48833470796945</v>
+        <v>-17.90012243490894</v>
       </c>
       <c r="F75">
-        <v>1.690136917134588</v>
+        <v>0.987285399942069</v>
       </c>
       <c r="G75">
-        <v>-9.458471426190481</v>
+        <v>-8.843934857735572</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.775152649433858</v>
       </c>
       <c r="E76">
-        <v>-16.85927985508995</v>
+        <v>-17.44410963081054</v>
       </c>
       <c r="F76">
-        <v>0.9896793817361595</v>
+        <v>0.9918049724917432</v>
       </c>
       <c r="G76">
-        <v>-7.461186196892783</v>
+        <v>-8.700839837346114</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.911074619087777</v>
       </c>
       <c r="E77">
-        <v>-16.73392263760962</v>
+        <v>-18.60002073516443</v>
       </c>
       <c r="F77">
-        <v>1.219993684206117</v>
+        <v>0.5136903600461329</v>
       </c>
       <c r="G77">
-        <v>-7.819536198791192</v>
+        <v>-8.48645221876845</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.058314369896394</v>
       </c>
       <c r="E78">
-        <v>-16.92048670977762</v>
+        <v>-18.50535751450809</v>
       </c>
       <c r="F78">
-        <v>1.008925669972803</v>
+        <v>0.8135866959838463</v>
       </c>
       <c r="G78">
-        <v>-7.359102214643816</v>
+        <v>-9.162962199718518</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.213767837246534</v>
       </c>
       <c r="E79">
-        <v>-17.02691490590589</v>
+        <v>-19.02398100023654</v>
       </c>
       <c r="F79">
-        <v>1.190326534042256</v>
+        <v>0.4709971324732491</v>
       </c>
       <c r="G79">
-        <v>-7.285015516020466</v>
+        <v>-8.479049838942641</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.374721584217518</v>
       </c>
       <c r="E80">
-        <v>-17.60386513685313</v>
+        <v>-18.66507679275862</v>
       </c>
       <c r="F80">
-        <v>0.4401247077383144</v>
+        <v>0.4648183400157677</v>
       </c>
       <c r="G80">
-        <v>-6.935246448159847</v>
+        <v>-8.21922829338402</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.534758497455973</v>
       </c>
       <c r="E81">
-        <v>-17.57891777354488</v>
+        <v>-20.46299871412795</v>
       </c>
       <c r="F81">
-        <v>1.15854539026645</v>
+        <v>0.409221633409476</v>
       </c>
       <c r="G81">
-        <v>-7.649102693338433</v>
+        <v>-7.58388494621479</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.687114796177854</v>
       </c>
       <c r="E82">
-        <v>-18.65738291541959</v>
+        <v>-20.59378104346947</v>
       </c>
       <c r="F82">
-        <v>1.033728646747426</v>
+        <v>0.5462940726529186</v>
       </c>
       <c r="G82">
-        <v>-6.907537181996148</v>
+        <v>-7.804360658039172</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.826985076450176</v>
       </c>
       <c r="E83">
-        <v>-20.34881777049855</v>
+        <v>-21.2402705212785</v>
       </c>
       <c r="F83">
-        <v>0.5713057980130469</v>
+        <v>0.620827258087207</v>
       </c>
       <c r="G83">
-        <v>-5.413484669577522</v>
+        <v>-7.454637937816104</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.947299591894657</v>
       </c>
       <c r="E84">
-        <v>-21.17361138388559</v>
+        <v>-21.69219411334797</v>
       </c>
       <c r="F84">
-        <v>0.9223016339272534</v>
+        <v>0.329167379235529</v>
       </c>
       <c r="G84">
-        <v>-5.683204746298563</v>
+        <v>-8.644461246812325</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.040151353709982</v>
       </c>
       <c r="E85">
-        <v>-21.39853163089856</v>
+        <v>-23.20729924751627</v>
       </c>
       <c r="F85">
-        <v>0.8213269609956049</v>
+        <v>0.2836750982085857</v>
       </c>
       <c r="G85">
-        <v>-6.408949160508671</v>
+        <v>-7.764521553019583</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.100250865744271</v>
       </c>
       <c r="E86">
-        <v>-21.32222684386932</v>
+        <v>-23.44180174552947</v>
       </c>
       <c r="F86">
-        <v>0.416319913684065</v>
+        <v>0.1644614318020977</v>
       </c>
       <c r="G86">
-        <v>-6.598279259899591</v>
+        <v>-7.532442379080055</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.122648554977502</v>
       </c>
       <c r="E87">
-        <v>-24.16737196493444</v>
+        <v>-24.51406740648768</v>
       </c>
       <c r="F87">
-        <v>0.3122405197267239</v>
+        <v>0.06365574582062025</v>
       </c>
       <c r="G87">
-        <v>-6.26940966602839</v>
+        <v>-7.120749556907369</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.101930462933112</v>
       </c>
       <c r="E88">
-        <v>-23.10388701507711</v>
+        <v>-25.46242496164801</v>
       </c>
       <c r="F88">
-        <v>-0.1739233387718891</v>
+        <v>-0.1154348015624245</v>
       </c>
       <c r="G88">
-        <v>-5.40045105178941</v>
+        <v>-7.27968553770224</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.036095516304096</v>
       </c>
       <c r="E89">
-        <v>-25.69589949606147</v>
+        <v>-26.42139725988233</v>
       </c>
       <c r="F89">
-        <v>0.3285692979707078</v>
+        <v>-0.3815784793056692</v>
       </c>
       <c r="G89">
-        <v>-6.105471450923681</v>
+        <v>-7.338682769757591</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.925621652418099</v>
       </c>
       <c r="E90">
-        <v>-27.85572800317581</v>
+        <v>-27.8621040945786</v>
       </c>
       <c r="F90">
-        <v>0.4653352412751146</v>
+        <v>-0.2590712241056503</v>
       </c>
       <c r="G90">
-        <v>-6.885124788695282</v>
+        <v>-7.948942113375764</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.771058287541733</v>
       </c>
       <c r="E91">
-        <v>-29.21679256549918</v>
+        <v>-28.9632885905498</v>
       </c>
       <c r="F91">
-        <v>-0.3707119557157453</v>
+        <v>-0.1906845248001343</v>
       </c>
       <c r="G91">
-        <v>-5.775125353741966</v>
+        <v>-7.14549919535896</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.575108782543237</v>
       </c>
       <c r="E92">
-        <v>-31.61840762106806</v>
+        <v>-31.30022118763011</v>
       </c>
       <c r="F92">
-        <v>-0.1783981794818121</v>
+        <v>-0.6495114306389609</v>
       </c>
       <c r="G92">
-        <v>-5.595412389142631</v>
+        <v>-7.308613084624391</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.345054251580174</v>
       </c>
       <c r="E93">
-        <v>-30.60203012207551</v>
+        <v>-32.09911645816728</v>
       </c>
       <c r="F93">
-        <v>0.2204980014992758</v>
+        <v>-0.6177924144183651</v>
       </c>
       <c r="G93">
-        <v>-6.686975395987744</v>
+        <v>-7.728847114288397</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.087551261907538</v>
       </c>
       <c r="E94">
-        <v>-33.80001129544826</v>
+        <v>-33.50365210672729</v>
       </c>
       <c r="F94">
-        <v>-0.7284482171865314</v>
+        <v>-0.8551685489971885</v>
       </c>
       <c r="G94">
-        <v>-7.365700131903584</v>
+        <v>-7.603970026001549</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.809741681711966</v>
       </c>
       <c r="E95">
-        <v>-35.99268256030323</v>
+        <v>-35.15380312851533</v>
       </c>
       <c r="F95">
-        <v>-0.7418644556422722</v>
+        <v>-0.968447791330021</v>
       </c>
       <c r="G95">
-        <v>-6.641260072635948</v>
+        <v>-7.672346033569656</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.523833991643608</v>
       </c>
       <c r="E96">
-        <v>-37.17081262237575</v>
+        <v>-37.97492469496976</v>
       </c>
       <c r="F96">
-        <v>-0.7241837817969196</v>
+        <v>-1.140732472131665</v>
       </c>
       <c r="G96">
-        <v>-6.215606679924155</v>
+        <v>-7.917869332944164</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.240909034467296</v>
       </c>
       <c r="E97">
-        <v>-37.13544297613884</v>
+        <v>-39.88190585586582</v>
       </c>
       <c r="F97">
-        <v>-1.823158105905954</v>
+        <v>-1.44169740201899</v>
       </c>
       <c r="G97">
-        <v>-6.861881448464058</v>
+        <v>-7.612021272753056</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.9695510322053758</v>
       </c>
       <c r="E98">
-        <v>-40.52356118767166</v>
+        <v>-41.04572594007411</v>
       </c>
       <c r="F98">
-        <v>-0.8156247742897486</v>
+        <v>-1.743389638485972</v>
       </c>
       <c r="G98">
-        <v>-6.818976778275104</v>
+        <v>-8.242865588534416</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.7237204519518031</v>
       </c>
       <c r="E99">
-        <v>-43.27810739350232</v>
+        <v>-42.60038050198839</v>
       </c>
       <c r="F99">
-        <v>-1.730030557381025</v>
+        <v>-1.994691457473258</v>
       </c>
       <c r="G99">
-        <v>-7.511837543643631</v>
+        <v>-8.42363792770632</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.5104391235514535</v>
       </c>
       <c r="E100">
-        <v>-44.58312529726977</v>
+        <v>-46.16709946414672</v>
       </c>
       <c r="F100">
-        <v>-1.849628586262412</v>
+        <v>-2.269381401711186</v>
       </c>
       <c r="G100">
-        <v>-7.21922173397299</v>
+        <v>-7.981484776026799</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.3390993571665009</v>
       </c>
       <c r="E101">
-        <v>-47.26344528564071</v>
+        <v>-47.83527381248528</v>
       </c>
       <c r="F101">
-        <v>-2.090215472894486</v>
+        <v>-2.448755250745988</v>
       </c>
       <c r="G101">
-        <v>-6.601030323242725</v>
+        <v>-8.889348921443293</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.2096856683283739</v>
       </c>
       <c r="E102">
-        <v>-49.69032582981688</v>
+        <v>-49.65314592609541</v>
       </c>
       <c r="F102">
-        <v>-2.359241869199473</v>
+        <v>-2.757748717501245</v>
       </c>
       <c r="G102">
-        <v>-6.974175153156137</v>
+        <v>-8.522073688771009</v>
       </c>
     </row>
   </sheetData>
